--- a/e_pod_line_simulator/configs/产线配置模板.xlsx
+++ b/e_pod_line_simulator/configs/产线配置模板.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,88 +416,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>工序名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>耗时(秒)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>模式</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>OEE</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>人员效率</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>切换时间(分钟)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>缓冲区容量</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>机台节拍(秒)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>清洗时间(分钟)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>抽检比例</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>缺陷率</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>返工时长(分钟)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>工种</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>洁净区</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>BOM(组件:用量;...)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>机台数量</t>
         </is>
       </c>
     </row>
@@ -562,6 +555,9 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -612,6 +608,9 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -662,6 +661,9 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -712,6 +714,9 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -728,12 +733,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>配置项</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>值</t>
         </is>
@@ -824,22 +829,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>原料名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>初始库存</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
@@ -878,17 +883,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>到货时间(分钟)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>原料</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>数量</t>
         </is>

--- a/e_pod_line_simulator/configs/产线配置模板.xlsx
+++ b/e_pod_line_simulator/configs/产线配置模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工序" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产线配置" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原料" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="到货计划" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="工序" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="产线配置" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="原料" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="到货计划" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,11 +505,16 @@
           <t>机台数量</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>最低机台节拍(秒)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>注油</t>
+          <t>零件装配</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -530,7 +535,7 @@
         <v>0.95</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
@@ -558,6 +563,7 @@
       <c r="Q2" t="n">
         <v>1</v>
       </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -583,7 +589,7 @@
         <v>0.95</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>100</v>
@@ -611,6 +617,7 @@
       <c r="Q3" t="n">
         <v>1</v>
       </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -664,6 +671,7 @@
       <c r="Q4" t="n">
         <v>1</v>
       </c>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -717,6 +725,7 @@
       <c r="Q5" t="n">
         <v>1</v>
       </c>
+      <c r="R5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -729,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,6 +822,18 @@
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>output_unit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -853,7 +874,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>棉芯</t>
+          <t>组件A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -905,7 +926,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>棉芯</t>
+          <t>组件A</t>
         </is>
       </c>
       <c r="C2" t="n">
